--- a/真靈光企劃書所有資訊(線上共編處)/真靈光利潤試算.xlsx
+++ b/真靈光企劃書所有資訊(線上共編處)/真靈光利潤試算.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Git\true-soul-light-cowork\真靈光企劃書所有資訊(線上共編處)\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{64AA9BE0-F000-4B48-8D85-3CEC7B8F2E29}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{37375794-3A9D-4052-A6C1-5230BDDBD3F9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="11805" yWindow="0" windowWidth="25335" windowHeight="16200" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="18570" windowHeight="16200" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="圖表" sheetId="1" r:id="rId1"/>
@@ -18,7 +18,6 @@
     <sheet name="客觀估計" sheetId="3" r:id="rId3"/>
     <sheet name="樂觀估計" sheetId="4" r:id="rId4"/>
     <sheet name="成本明細" sheetId="5" r:id="rId5"/>
-    <sheet name="工作表1" sheetId="6" r:id="rId6"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -4209,14 +4208,4 @@
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
-  <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.25"/>
-  <sheetData/>
-  <phoneticPr fontId="1" type="noConversion"/>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
 </file>